--- a/Configs/skill_pool_config.xlsx
+++ b/Configs/skill_pool_config.xlsx
@@ -1,40 +1,519 @@
 
 <file path=xl/workbook.xml><?xml version="1.0" encoding="utf-8"?>
-<workbook xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
+<workbook xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:dbsheet="http://web.wps.cn/et/2021/dbsheet">
+  <fileVersion appName="xl" lastEdited="3" lowestEdited="5" rupBuild="9302"/>
   <workbookPr/>
-  <workbookProtection/>
   <bookViews>
-    <workbookView activeTab="0" autoFilterDateGrouping="1" firstSheet="0" minimized="0" showHorizontalScroll="1" showSheetTabs="1" showVerticalScroll="1" tabRatio="600" visibility="visible"/>
+    <workbookView windowWidth="28800" windowHeight="12375"/>
   </bookViews>
   <sheets>
-    <sheet name="skill_pool_config" sheetId="1" state="visible" r:id="rId1"/>
+    <sheet name="skill_pool_config" sheetId="1" r:id="rId1"/>
   </sheets>
-  <definedNames/>
-  <calcPr calcId="124519" fullCalcOnLoad="1"/>
+  <calcPr calcId="191029"/>
+  <extLst>
+    <ext xmlns:xcalcf="http://schemas.microsoft.com/office/spreadsheetml/2018/calcfeatures" uri="{B58B0392-4F1F-4190-BB64-5DF3571DCE5F}">
+      <xcalcf:calcFeatures>
+        <xcalcf:feature name="microsoft.com:RD"/>
+        <xcalcf:feature name="microsoft.com:Single"/>
+        <xcalcf:feature name="microsoft.com:FV"/>
+        <xcalcf:feature name="microsoft.com:CNMTM"/>
+        <xcalcf:feature name="microsoft.com:LET_WF"/>
+        <xcalcf:feature name="microsoft.com:LAMBDA_WF"/>
+        <xcalcf:feature name="microsoft.com:ARRAYTEXT_WF"/>
+      </xcalcf:calcFeatures>
+    </ext>
+  </extLst>
 </workbook>
 </file>
 
+<file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="42" uniqueCount="40">
+  <si>
+    <t>id</t>
+  </si>
+  <si>
+    <t>name</t>
+  </si>
+  <si>
+    <t>desList</t>
+  </si>
+  <si>
+    <t>icon</t>
+  </si>
+  <si>
+    <t>dragHint</t>
+  </si>
+  <si>
+    <t>int</t>
+  </si>
+  <si>
+    <t>string</t>
+  </si>
+  <si>
+    <t>string[]</t>
+  </si>
+  <si>
+    <t>烈焰圣弹</t>
+  </si>
+  <si>
+    <t>发射炽热的火焰弹|[升级效果]额外发射一枚|[6级]附加灼烧，每秒造成30%火伤，持续5秒|[10级]命中后会发生爆炸</t>
+  </si>
+  <si>
+    <t>Icon/commet-128</t>
+  </si>
+  <si>
+    <t>松开发射弹幕</t>
+  </si>
+  <si>
+    <t>治愈圣火</t>
+  </si>
+  <si>
+    <t>恢复生命最大生命值的10%|[升级效果]多恢复最大生命值的5%|[6级]附加持续恢复，每秒恢复已损失生命值的10%，持续10秒|[10级]附加减伤</t>
+  </si>
+  <si>
+    <t>Icon/potion-pink-1-128</t>
+  </si>
+  <si>
+    <t>松开施加效果</t>
+  </si>
+  <si>
+    <t>急冻冰锥</t>
+  </si>
+  <si>
+    <t>发射冰棱并冰冻|[升级效果]额外发射一枚|[6级]子弹变为穿刺效果|[10级]冰冻时间提升至10秒</t>
+  </si>
+  <si>
+    <t>Icon/skull-128</t>
+  </si>
+  <si>
+    <t>松开发射冰锥</t>
+  </si>
+  <si>
+    <t>血能交换</t>
+  </si>
+  <si>
+    <t>消耗当前生命值的25%换取随机一个非满级技能的10点经验|[升级效果]获得经验值提升5点|[6级]随机三个非满级技能|[10级]改为所有非满级技能</t>
+  </si>
+  <si>
+    <t>Icon/solar-system-1-128</t>
+  </si>
+  <si>
+    <t>松开消耗生命</t>
+  </si>
+  <si>
+    <t>闪电连锁</t>
+  </si>
+  <si>
+    <t>发射一枚闪电，命中后弹射向另一名敌人，每次弹射伤害递减10%，最多递减50%|[升级效果]次数弹射加一次|[6级]减速50%，持续3秒|[10级]闪电伤害不衰减</t>
+  </si>
+  <si>
+    <t>Icon/satellite-128</t>
+  </si>
+  <si>
+    <t>松开发射闪电</t>
+  </si>
+  <si>
+    <t>电磁盾牌</t>
+  </si>
+  <si>
+    <t>为自身附加一共最大生命值10%的护盾，护盾被攻击时会反射一枚子弹造成30%电伤|[升级效果]护盾提升5%，反射子弹数量加一|[6级]反射的子弹具有穿透效果|[10级]护盾破裂时，对敌人造成击退，并且恢复自身已损失生命值的50%</t>
+  </si>
+  <si>
+    <t>Icon/gem-2-128</t>
+  </si>
+  <si>
+    <t>松开激活护盾</t>
+  </si>
+  <si>
+    <t>超暴风</t>
+  </si>
+  <si>
+    <t>对所有敌人造成100%的风伤并击退|[升级效果]+10%击退|[6级]附加减速|[10级]附加易伤</t>
+  </si>
+  <si>
+    <t>Icon/black-hole-128</t>
+  </si>
+  <si>
+    <t>松开释放风暴</t>
+  </si>
+  <si>
+    <t>风影守卫</t>
+  </si>
+  <si>
+    <t>召唤风影战斗，继承主角25%属性|[升级效果]持续+2秒|[6级]追踪弹|[10级]额外两个风影</t>
+  </si>
+  <si>
+    <t>Icon/alien-128</t>
+  </si>
+  <si>
+    <t>松开召唤守卫</t>
+  </si>
+</sst>
+</file>
+
 <file path=xl/styles.xml><?xml version="1.0" encoding="utf-8"?>
-<styleSheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
-  <numFmts count="0"/>
-  <fonts count="1">
-    <font>
-      <name val="Calibri"/>
-      <family val="2"/>
+<styleSheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:xr9="http://schemas.microsoft.com/office/spreadsheetml/2016/revision9" mc:Ignorable="xr9">
+  <numFmts count="4">
+    <numFmt numFmtId="41" formatCode="_ * #,##0_ ;_ * \-#,##0_ ;_ * &quot;-&quot;_ ;_ @_ "/>
+    <numFmt numFmtId="42" formatCode="_ &quot;￥&quot;* #,##0_ ;_ &quot;￥&quot;* \-#,##0_ ;_ &quot;￥&quot;* &quot;-&quot;_ ;_ @_ "/>
+    <numFmt numFmtId="43" formatCode="_ * #,##0.00_ ;_ * \-#,##0.00_ ;_ * &quot;-&quot;??_ ;_ @_ "/>
+    <numFmt numFmtId="44" formatCode="_ &quot;￥&quot;* #,##0.00_ ;_ &quot;￥&quot;* \-#,##0.00_ ;_ &quot;￥&quot;* &quot;-&quot;??_ ;_ @_ "/>
+  </numFmts>
+  <fonts count="21">
+    <font>
+      <sz val="11"/>
       <color theme="1"/>
-      <sz val="11"/>
+      <name val="宋体"/>
+      <charset val="134"/>
+      <scheme val="minor"/>
+    </font>
+    <font>
+      <sz val="11"/>
+      <color theme="1"/>
+      <name val="宋体"/>
+      <charset val="134"/>
+      <scheme val="minor"/>
+    </font>
+    <font>
+      <u/>
+      <sz val="11"/>
+      <color rgb="FF0000FF"/>
+      <name val="宋体"/>
+      <charset val="0"/>
+      <scheme val="minor"/>
+    </font>
+    <font>
+      <u/>
+      <sz val="11"/>
+      <color rgb="FF800080"/>
+      <name val="宋体"/>
+      <charset val="0"/>
+      <scheme val="minor"/>
+    </font>
+    <font>
+      <sz val="11"/>
+      <color rgb="FFFF0000"/>
+      <name val="宋体"/>
+      <charset val="0"/>
+      <scheme val="minor"/>
+    </font>
+    <font>
+      <b/>
+      <sz val="18"/>
+      <color theme="3"/>
+      <name val="宋体"/>
+      <charset val="134"/>
+      <scheme val="minor"/>
+    </font>
+    <font>
+      <i/>
+      <sz val="11"/>
+      <color rgb="FF7F7F7F"/>
+      <name val="宋体"/>
+      <charset val="0"/>
+      <scheme val="minor"/>
+    </font>
+    <font>
+      <b/>
+      <sz val="15"/>
+      <color theme="3"/>
+      <name val="宋体"/>
+      <charset val="134"/>
+      <scheme val="minor"/>
+    </font>
+    <font>
+      <b/>
+      <sz val="13"/>
+      <color theme="3"/>
+      <name val="宋体"/>
+      <charset val="134"/>
+      <scheme val="minor"/>
+    </font>
+    <font>
+      <b/>
+      <sz val="11"/>
+      <color theme="3"/>
+      <name val="宋体"/>
+      <charset val="134"/>
+      <scheme val="minor"/>
+    </font>
+    <font>
+      <sz val="11"/>
+      <color rgb="FF3F3F76"/>
+      <name val="宋体"/>
+      <charset val="0"/>
+      <scheme val="minor"/>
+    </font>
+    <font>
+      <b/>
+      <sz val="11"/>
+      <color rgb="FF3F3F3F"/>
+      <name val="宋体"/>
+      <charset val="0"/>
+      <scheme val="minor"/>
+    </font>
+    <font>
+      <b/>
+      <sz val="11"/>
+      <color rgb="FFFA7D00"/>
+      <name val="宋体"/>
+      <charset val="0"/>
+      <scheme val="minor"/>
+    </font>
+    <font>
+      <b/>
+      <sz val="11"/>
+      <color rgb="FFFFFFFF"/>
+      <name val="宋体"/>
+      <charset val="0"/>
+      <scheme val="minor"/>
+    </font>
+    <font>
+      <sz val="11"/>
+      <color rgb="FFFA7D00"/>
+      <name val="宋体"/>
+      <charset val="0"/>
+      <scheme val="minor"/>
+    </font>
+    <font>
+      <b/>
+      <sz val="11"/>
+      <color theme="1"/>
+      <name val="宋体"/>
+      <charset val="0"/>
+      <scheme val="minor"/>
+    </font>
+    <font>
+      <sz val="11"/>
+      <color rgb="FF006100"/>
+      <name val="宋体"/>
+      <charset val="0"/>
+      <scheme val="minor"/>
+    </font>
+    <font>
+      <sz val="11"/>
+      <color rgb="FF9C0006"/>
+      <name val="宋体"/>
+      <charset val="0"/>
+      <scheme val="minor"/>
+    </font>
+    <font>
+      <sz val="11"/>
+      <color rgb="FF9C6500"/>
+      <name val="宋体"/>
+      <charset val="0"/>
+      <scheme val="minor"/>
+    </font>
+    <font>
+      <sz val="11"/>
+      <color theme="0"/>
+      <name val="宋体"/>
+      <charset val="0"/>
+      <scheme val="minor"/>
+    </font>
+    <font>
+      <sz val="11"/>
+      <color theme="1"/>
+      <name val="宋体"/>
+      <charset val="0"/>
       <scheme val="minor"/>
     </font>
   </fonts>
-  <fills count="2">
-    <fill>
-      <patternFill/>
+  <fills count="33">
+    <fill>
+      <patternFill patternType="none"/>
     </fill>
     <fill>
       <patternFill patternType="gray125"/>
     </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FFFFFFCC"/>
+        <bgColor indexed="64"/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FFFFCC99"/>
+        <bgColor indexed="64"/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FFF2F2F2"/>
+        <bgColor indexed="64"/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FFA5A5A5"/>
+        <bgColor indexed="64"/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FFC6EFCE"/>
+        <bgColor indexed="64"/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FFFFC7CE"/>
+        <bgColor indexed="64"/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FFFFEB9C"/>
+        <bgColor indexed="64"/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor theme="4"/>
+        <bgColor indexed="64"/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor theme="4" tint="0.799981688894314"/>
+        <bgColor indexed="64"/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor theme="4" tint="0.599993896298105"/>
+        <bgColor indexed="64"/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor theme="4" tint="0.399975585192419"/>
+        <bgColor indexed="64"/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor theme="5"/>
+        <bgColor indexed="64"/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor theme="5" tint="0.799981688894314"/>
+        <bgColor indexed="64"/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor theme="5" tint="0.599993896298105"/>
+        <bgColor indexed="64"/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor theme="5" tint="0.399975585192419"/>
+        <bgColor indexed="64"/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor theme="6"/>
+        <bgColor indexed="64"/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor theme="6" tint="0.799981688894314"/>
+        <bgColor indexed="64"/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor theme="6" tint="0.599993896298105"/>
+        <bgColor indexed="64"/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor theme="6" tint="0.399975585192419"/>
+        <bgColor indexed="64"/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor theme="7"/>
+        <bgColor indexed="64"/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor theme="7" tint="0.799981688894314"/>
+        <bgColor indexed="64"/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor theme="7" tint="0.599993896298105"/>
+        <bgColor indexed="64"/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor theme="7" tint="0.399975585192419"/>
+        <bgColor indexed="64"/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor theme="8"/>
+        <bgColor indexed="64"/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor theme="8" tint="0.799981688894314"/>
+        <bgColor indexed="64"/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor theme="8" tint="0.599993896298105"/>
+        <bgColor indexed="64"/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor theme="8" tint="0.399975585192419"/>
+        <bgColor indexed="64"/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor theme="9"/>
+        <bgColor indexed="64"/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor theme="9" tint="0.799981688894314"/>
+        <bgColor indexed="64"/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor theme="9" tint="0.599993896298105"/>
+        <bgColor indexed="64"/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor theme="9" tint="0.399975585192419"/>
+        <bgColor indexed="64"/>
+      </patternFill>
+    </fill>
   </fills>
-  <borders count="1">
+  <borders count="9">
     <border>
       <left/>
       <right/>
@@ -42,17 +521,312 @@
       <bottom/>
       <diagonal/>
     </border>
+    <border>
+      <left style="thin">
+        <color rgb="FFB2B2B2"/>
+      </left>
+      <right style="thin">
+        <color rgb="FFB2B2B2"/>
+      </right>
+      <top style="thin">
+        <color rgb="FFB2B2B2"/>
+      </top>
+      <bottom style="thin">
+        <color rgb="FFB2B2B2"/>
+      </bottom>
+      <diagonal/>
+    </border>
+    <border>
+      <left/>
+      <right/>
+      <top/>
+      <bottom style="medium">
+        <color theme="4"/>
+      </bottom>
+      <diagonal/>
+    </border>
+    <border>
+      <left/>
+      <right/>
+      <top/>
+      <bottom style="medium">
+        <color theme="4" tint="0.499984740745262"/>
+      </bottom>
+      <diagonal/>
+    </border>
+    <border>
+      <left style="thin">
+        <color rgb="FF7F7F7F"/>
+      </left>
+      <right style="thin">
+        <color rgb="FF7F7F7F"/>
+      </right>
+      <top style="thin">
+        <color rgb="FF7F7F7F"/>
+      </top>
+      <bottom style="thin">
+        <color rgb="FF7F7F7F"/>
+      </bottom>
+      <diagonal/>
+    </border>
+    <border>
+      <left style="thin">
+        <color rgb="FF3F3F3F"/>
+      </left>
+      <right style="thin">
+        <color rgb="FF3F3F3F"/>
+      </right>
+      <top style="thin">
+        <color rgb="FF3F3F3F"/>
+      </top>
+      <bottom style="thin">
+        <color rgb="FF3F3F3F"/>
+      </bottom>
+      <diagonal/>
+    </border>
+    <border>
+      <left style="double">
+        <color rgb="FF3F3F3F"/>
+      </left>
+      <right style="double">
+        <color rgb="FF3F3F3F"/>
+      </right>
+      <top style="double">
+        <color rgb="FF3F3F3F"/>
+      </top>
+      <bottom style="double">
+        <color rgb="FF3F3F3F"/>
+      </bottom>
+      <diagonal/>
+    </border>
+    <border>
+      <left/>
+      <right/>
+      <top/>
+      <bottom style="double">
+        <color rgb="FFFF8001"/>
+      </bottom>
+      <diagonal/>
+    </border>
+    <border>
+      <left/>
+      <right/>
+      <top style="thin">
+        <color theme="4"/>
+      </top>
+      <bottom style="double">
+        <color theme="4"/>
+      </bottom>
+      <diagonal/>
+    </border>
   </borders>
-  <cellStyleXfs count="1">
-    <xf borderId="0" fillId="0" fontId="0" numFmtId="0"/>
+  <cellStyleXfs count="49">
+    <xf numFmtId="0" fontId="0" fillId="0" borderId="0"/>
+    <xf numFmtId="43" fontId="1" fillId="0" borderId="0" applyFont="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="44" fontId="1" fillId="0" borderId="0" applyFont="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="9" fontId="1" fillId="0" borderId="0" applyFont="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="41" fontId="1" fillId="0" borderId="0" applyFont="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="42" fontId="1" fillId="0" borderId="0" applyFont="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="2" fillId="0" borderId="0" applyNumberFormat="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="3" fillId="0" borderId="0" applyNumberFormat="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="1" fillId="2" borderId="1" applyNumberFormat="0" applyFont="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="4" fillId="0" borderId="0" applyNumberFormat="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="5" fillId="0" borderId="0" applyNumberFormat="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="6" fillId="0" borderId="0" applyNumberFormat="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="7" fillId="0" borderId="2" applyNumberFormat="0" applyFill="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="8" fillId="0" borderId="2" applyNumberFormat="0" applyFill="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="9" fillId="0" borderId="3" applyNumberFormat="0" applyFill="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="9" fillId="0" borderId="0" applyNumberFormat="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="10" fillId="3" borderId="4" applyNumberFormat="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="11" fillId="4" borderId="5" applyNumberFormat="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="12" fillId="4" borderId="4" applyNumberFormat="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="13" fillId="5" borderId="6" applyNumberFormat="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="14" fillId="0" borderId="7" applyNumberFormat="0" applyFill="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="15" fillId="0" borderId="8" applyNumberFormat="0" applyFill="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="16" fillId="6" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="17" fillId="7" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="18" fillId="8" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="19" fillId="9" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="20" fillId="10" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="20" fillId="11" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="19" fillId="12" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="19" fillId="13" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="20" fillId="14" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="20" fillId="15" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="19" fillId="16" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="19" fillId="17" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="20" fillId="18" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="20" fillId="19" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="19" fillId="20" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="19" fillId="21" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="20" fillId="22" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="20" fillId="23" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="19" fillId="24" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="19" fillId="25" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="20" fillId="26" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="20" fillId="27" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="19" fillId="28" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="19" fillId="29" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="20" fillId="30" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="20" fillId="31" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="19" fillId="32" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
   </cellStyleXfs>
   <cellXfs count="1">
-    <xf borderId="0" fillId="0" fontId="0" numFmtId="0" pivotButton="0" quotePrefix="0" xfId="0"/>
+    <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0"/>
   </cellXfs>
-  <cellStyles count="1">
-    <cellStyle builtinId="0" hidden="0" name="Normal" xfId="0"/>
+  <cellStyles count="49">
+    <cellStyle name="常规" xfId="0" builtinId="0"/>
+    <cellStyle name="千位分隔" xfId="1" builtinId="3"/>
+    <cellStyle name="货币" xfId="2" builtinId="4"/>
+    <cellStyle name="百分比" xfId="3" builtinId="5"/>
+    <cellStyle name="千位分隔[0]" xfId="4" builtinId="6"/>
+    <cellStyle name="货币[0]" xfId="5" builtinId="7"/>
+    <cellStyle name="超链接" xfId="6" builtinId="8"/>
+    <cellStyle name="已访问的超链接" xfId="7" builtinId="9"/>
+    <cellStyle name="注释" xfId="8" builtinId="10"/>
+    <cellStyle name="警告文本" xfId="9" builtinId="11"/>
+    <cellStyle name="标题" xfId="10" builtinId="15"/>
+    <cellStyle name="解释性文本" xfId="11" builtinId="53"/>
+    <cellStyle name="标题 1" xfId="12" builtinId="16"/>
+    <cellStyle name="标题 2" xfId="13" builtinId="17"/>
+    <cellStyle name="标题 3" xfId="14" builtinId="18"/>
+    <cellStyle name="标题 4" xfId="15" builtinId="19"/>
+    <cellStyle name="输入" xfId="16" builtinId="20"/>
+    <cellStyle name="输出" xfId="17" builtinId="21"/>
+    <cellStyle name="计算" xfId="18" builtinId="22"/>
+    <cellStyle name="检查单元格" xfId="19" builtinId="23"/>
+    <cellStyle name="链接单元格" xfId="20" builtinId="24"/>
+    <cellStyle name="汇总" xfId="21" builtinId="25"/>
+    <cellStyle name="好" xfId="22" builtinId="26"/>
+    <cellStyle name="差" xfId="23" builtinId="27"/>
+    <cellStyle name="适中" xfId="24" builtinId="28"/>
+    <cellStyle name="强调文字颜色 1" xfId="25" builtinId="29"/>
+    <cellStyle name="20% - 强调文字颜色 1" xfId="26" builtinId="30"/>
+    <cellStyle name="40% - 强调文字颜色 1" xfId="27" builtinId="31"/>
+    <cellStyle name="60% - 强调文字颜色 1" xfId="28" builtinId="32"/>
+    <cellStyle name="强调文字颜色 2" xfId="29" builtinId="33"/>
+    <cellStyle name="20% - 强调文字颜色 2" xfId="30" builtinId="34"/>
+    <cellStyle name="40% - 强调文字颜色 2" xfId="31" builtinId="35"/>
+    <cellStyle name="60% - 强调文字颜色 2" xfId="32" builtinId="36"/>
+    <cellStyle name="强调文字颜色 3" xfId="33" builtinId="37"/>
+    <cellStyle name="20% - 强调文字颜色 3" xfId="34" builtinId="38"/>
+    <cellStyle name="40% - 强调文字颜色 3" xfId="35" builtinId="39"/>
+    <cellStyle name="60% - 强调文字颜色 3" xfId="36" builtinId="40"/>
+    <cellStyle name="强调文字颜色 4" xfId="37" builtinId="41"/>
+    <cellStyle name="20% - 强调文字颜色 4" xfId="38" builtinId="42"/>
+    <cellStyle name="40% - 强调文字颜色 4" xfId="39" builtinId="43"/>
+    <cellStyle name="60% - 强调文字颜色 4" xfId="40" builtinId="44"/>
+    <cellStyle name="强调文字颜色 5" xfId="41" builtinId="45"/>
+    <cellStyle name="20% - 强调文字颜色 5" xfId="42" builtinId="46"/>
+    <cellStyle name="40% - 强调文字颜色 5" xfId="43" builtinId="47"/>
+    <cellStyle name="60% - 强调文字颜色 5" xfId="44" builtinId="48"/>
+    <cellStyle name="强调文字颜色 6" xfId="45" builtinId="49"/>
+    <cellStyle name="20% - 强调文字颜色 6" xfId="46" builtinId="50"/>
+    <cellStyle name="40% - 强调文字颜色 6" xfId="47" builtinId="51"/>
+    <cellStyle name="60% - 强调文字颜色 6" xfId="48" builtinId="52"/>
   </cellStyles>
-  <tableStyles count="0" defaultPivotStyle="PivotStyleLight16" defaultTableStyle="TableStyleMedium9"/>
+  <tableStyles count="0" defaultTableStyle="TableStyleMedium9" defaultPivotStyle="PivotStyleLight16"/>
+  <extLst>
+    <ext xmlns:x14="http://schemas.microsoft.com/office/spreadsheetml/2009/9/main" uri="{EB79DEF2-80B8-43e5-95BD-54CBDDF9020C}">
+      <x14:slicerStyles defaultSlicerStyle="SlicerStyleLight1"/>
+    </ext>
+  </extLst>
 </styleSheet>
 </file>
 
@@ -335,274 +1109,192 @@
     </a:fmtScheme>
   </a:themeElements>
   <a:objectDefaults/>
-  <a:extraClrSchemeLst/>
 </a:theme>
 </file>
 
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
-<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
-  <sheetPr>
-    <outlinePr summaryBelow="1" summaryRight="1"/>
-    <pageSetUpPr/>
-  </sheetPr>
+<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:xdr="http://schemas.openxmlformats.org/drawingml/2006/spreadsheetDrawing" xmlns:x14="http://schemas.microsoft.com/office/spreadsheetml/2009/9/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:etc="http://www.wps.cn/officeDocument/2017/etCustomData">
+  <sheetPr/>
   <dimension ref="A1:E10"/>
-  <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
+  <sheetFormatPr defaultColWidth="9" defaultRowHeight="13.5" outlineLevelCol="4"/>
+  <cols>
+    <col min="3" max="3" width="50.125" customWidth="1"/>
+    <col min="4" max="4" width="26" customWidth="1"/>
+    <col min="5" max="5" width="12.875" customWidth="1"/>
+  </cols>
   <sheetData>
-    <row r="1">
-      <c r="A1" t="inlineStr">
-        <is>
-          <t>id</t>
-        </is>
-      </c>
-      <c r="B1" t="inlineStr">
-        <is>
-          <t>name</t>
-        </is>
-      </c>
-      <c r="C1" t="inlineStr">
-        <is>
-          <t>desList</t>
-        </is>
-      </c>
-      <c r="D1" t="inlineStr">
-        <is>
-          <t>icon</t>
-        </is>
-      </c>
-      <c r="E1" t="inlineStr">
-        <is>
-          <t>dragHint</t>
-        </is>
+    <row r="1" spans="1:5">
+      <c r="A1" t="s">
+        <v>0</v>
+      </c>
+      <c r="B1" t="s">
+        <v>1</v>
+      </c>
+      <c r="C1" t="s">
+        <v>2</v>
+      </c>
+      <c r="D1" t="s">
+        <v>3</v>
+      </c>
+      <c r="E1" t="s">
+        <v>4</v>
       </c>
     </row>
-    <row r="2">
-      <c r="A2" t="inlineStr">
-        <is>
-          <t>int</t>
-        </is>
-      </c>
-      <c r="B2" t="inlineStr">
-        <is>
-          <t>string</t>
-        </is>
-      </c>
-      <c r="C2" t="inlineStr">
-        <is>
-          <t>string[]</t>
-        </is>
-      </c>
-      <c r="D2" t="inlineStr">
-        <is>
-          <t>string</t>
-        </is>
-      </c>
-      <c r="E2" t="inlineStr">
-        <is>
-          <t>string</t>
-        </is>
+    <row r="2" spans="1:5">
+      <c r="A2" t="s">
+        <v>5</v>
+      </c>
+      <c r="B2" t="s">
+        <v>6</v>
+      </c>
+      <c r="C2" t="s">
+        <v>7</v>
+      </c>
+      <c r="D2" t="s">
+        <v>6</v>
+      </c>
+      <c r="E2" t="s">
+        <v>6</v>
       </c>
     </row>
-    <row r="3">
-      <c r="A3" t="n">
+    <row r="3" spans="1:5">
+      <c r="A3">
         <v>1001</v>
       </c>
-      <c r="B3" t="inlineStr">
-        <is>
-          <t>烈焰圣弹</t>
-        </is>
-      </c>
-      <c r="C3" t="inlineStr">
-        <is>
-          <t>发射炽热的火焰弹|[升级效果]额外发射一枚|[6级]附加灼烧，每秒造成30%火伤，持续5秒|[10级]命中后会发生爆炸</t>
-        </is>
-      </c>
-      <c r="D3" t="inlineStr">
-        <is>
-          <t>Icon/commet-128</t>
-        </is>
-      </c>
-      <c r="E3" t="inlineStr">
-        <is>
-          <t>松开发射弹幕</t>
-        </is>
+      <c r="B3" t="s">
+        <v>8</v>
+      </c>
+      <c r="C3" t="s">
+        <v>9</v>
+      </c>
+      <c r="D3" t="s">
+        <v>10</v>
+      </c>
+      <c r="E3" t="s">
+        <v>11</v>
       </c>
     </row>
-    <row r="4">
-      <c r="A4" t="n">
+    <row r="4" spans="1:5">
+      <c r="A4">
         <v>1002</v>
       </c>
-      <c r="B4" t="inlineStr">
-        <is>
-          <t>治愈圣火</t>
-        </is>
-      </c>
-      <c r="C4" t="inlineStr">
-        <is>
-          <t>恢复生命最大生命值的10%|[升级效果]多恢复最大生命值的5%|[6级]附加持续恢复，每秒恢复已损失生命值的10%，持续10秒|[10级]附加减伤</t>
-        </is>
-      </c>
-      <c r="D4" t="inlineStr">
-        <is>
-          <t>Icon/potion-pink-1-128</t>
-        </is>
-      </c>
-      <c r="E4" t="inlineStr">
-        <is>
-          <t>松开施加效果</t>
-        </is>
+      <c r="B4" t="s">
+        <v>12</v>
+      </c>
+      <c r="C4" t="s">
+        <v>13</v>
+      </c>
+      <c r="D4" t="s">
+        <v>14</v>
+      </c>
+      <c r="E4" t="s">
+        <v>15</v>
       </c>
     </row>
-    <row r="5">
-      <c r="A5" t="n">
+    <row r="5" spans="1:5">
+      <c r="A5">
         <v>1003</v>
       </c>
-      <c r="B5" t="inlineStr">
-        <is>
-          <t>急冻冰锥</t>
-        </is>
-      </c>
-      <c r="C5" t="inlineStr">
-        <is>
-          <t>发射冰棱并冰冻|[升级效果]额外发射一枚|[6级]子弹变为穿刺效果|[10级]冰冻时间提升至10秒</t>
-        </is>
-      </c>
-      <c r="D5" t="inlineStr">
-        <is>
-          <t>Icon/skull-128</t>
-        </is>
-      </c>
-      <c r="E5" t="inlineStr">
-        <is>
-          <t>松开发射冰锥</t>
-        </is>
+      <c r="B5" t="s">
+        <v>16</v>
+      </c>
+      <c r="C5" t="s">
+        <v>17</v>
+      </c>
+      <c r="D5" t="s">
+        <v>18</v>
+      </c>
+      <c r="E5" t="s">
+        <v>19</v>
       </c>
     </row>
-    <row r="6">
-      <c r="A6" t="n">
+    <row r="6" spans="1:5">
+      <c r="A6">
         <v>1004</v>
       </c>
-      <c r="B6" t="inlineStr">
-        <is>
-          <t>血能交换</t>
-        </is>
-      </c>
-      <c r="C6" t="inlineStr">
-        <is>
-          <t>消耗当前生命值的25%换取随机一个非满级技能的10点经验|[升级效果]获得经验值提升5点|[6级]随机三个非满级技能|[10级]改为所有非满级技能</t>
-        </is>
-      </c>
-      <c r="D6" t="inlineStr">
-        <is>
-          <t>Icon/solar-system-1-128</t>
-        </is>
-      </c>
-      <c r="E6" t="inlineStr">
-        <is>
-          <t>松开消耗生命</t>
-        </is>
+      <c r="B6" t="s">
+        <v>20</v>
+      </c>
+      <c r="C6" t="s">
+        <v>21</v>
+      </c>
+      <c r="D6" t="s">
+        <v>22</v>
+      </c>
+      <c r="E6" t="s">
+        <v>23</v>
       </c>
     </row>
-    <row r="7">
-      <c r="A7" t="n">
+    <row r="7" spans="1:5">
+      <c r="A7">
         <v>1005</v>
       </c>
-      <c r="B7" t="inlineStr">
-        <is>
-          <t>闪电连锁</t>
-        </is>
-      </c>
-      <c r="C7" t="inlineStr">
-        <is>
-          <t>发射一枚闪电，命中后弹射向另一名敌人，每次弹射伤害递减10%，最多递减50%|[升级效果]次数弹射加一次|[6级]减速50%，持续3秒|[10级]闪电伤害不衰减</t>
-        </is>
-      </c>
-      <c r="D7" t="inlineStr">
-        <is>
-          <t>Icon/satellite-128</t>
-        </is>
-      </c>
-      <c r="E7" t="inlineStr">
-        <is>
-          <t>松开发射闪电</t>
-        </is>
+      <c r="B7" t="s">
+        <v>24</v>
+      </c>
+      <c r="C7" t="s">
+        <v>25</v>
+      </c>
+      <c r="D7" t="s">
+        <v>26</v>
+      </c>
+      <c r="E7" t="s">
+        <v>27</v>
       </c>
     </row>
-    <row r="8">
-      <c r="A8" t="n">
+    <row r="8" spans="1:5">
+      <c r="A8">
         <v>1006</v>
       </c>
-      <c r="B8" t="inlineStr">
-        <is>
-          <t>电磁盾牌</t>
-        </is>
-      </c>
-      <c r="C8" t="inlineStr">
-        <is>
-          <t>为自身附加一共最大生命值10%的护盾，护盾被攻击时会反射一枚子弹造成30%电伤|[升级效果]护盾提升5%，反射子弹数量加一|[6级]反射的子弹具有穿透效果|[10级]护盾破裂时，对敌人造成击退，并且恢复自身已损失生命值的50%</t>
-        </is>
-      </c>
-      <c r="D8" t="inlineStr">
-        <is>
-          <t>Icon/gem-2-128</t>
-        </is>
-      </c>
-      <c r="E8" t="inlineStr">
-        <is>
-          <t>松开激活护盾</t>
-        </is>
+      <c r="B8" t="s">
+        <v>28</v>
+      </c>
+      <c r="C8" t="s">
+        <v>29</v>
+      </c>
+      <c r="D8" t="s">
+        <v>30</v>
+      </c>
+      <c r="E8" t="s">
+        <v>31</v>
       </c>
     </row>
-    <row r="9">
-      <c r="A9" t="n">
+    <row r="9" spans="1:5">
+      <c r="A9">
         <v>1007</v>
       </c>
-      <c r="B9" t="inlineStr">
-        <is>
-          <t>超暴风</t>
-        </is>
-      </c>
-      <c r="C9" t="inlineStr">
-        <is>
-          <t>对所有敌人造成100%的风伤并击退|[升级效果]+10%击退|[6级]附加减速|[10级]附加易伤</t>
-        </is>
-      </c>
-      <c r="D9" t="inlineStr">
-        <is>
-          <t>Icon/black-hole-128</t>
-        </is>
-      </c>
-      <c r="E9" t="inlineStr">
-        <is>
-          <t>松开释放风暴</t>
-        </is>
+      <c r="B9" t="s">
+        <v>32</v>
+      </c>
+      <c r="C9" t="s">
+        <v>33</v>
+      </c>
+      <c r="D9" t="s">
+        <v>34</v>
+      </c>
+      <c r="E9" t="s">
+        <v>35</v>
       </c>
     </row>
-    <row r="10">
-      <c r="A10" t="n">
+    <row r="10" spans="1:5">
+      <c r="A10">
         <v>1008</v>
       </c>
-      <c r="B10" t="inlineStr">
-        <is>
-          <t>风影守卫</t>
-        </is>
-      </c>
-      <c r="C10" t="inlineStr">
-        <is>
-          <t>召唤风影战斗，继承主角25%属性|[升级效果]持续+2秒|[6级]追踪弹|[10级]额外两个风影</t>
-        </is>
-      </c>
-      <c r="D10" t="inlineStr">
-        <is>
-          <t>Icon/alien-128</t>
-        </is>
-      </c>
-      <c r="E10" t="inlineStr">
-        <is>
-          <t>松开召唤守卫</t>
-        </is>
+      <c r="B10" t="s">
+        <v>36</v>
+      </c>
+      <c r="C10" t="s">
+        <v>37</v>
+      </c>
+      <c r="D10" t="s">
+        <v>38</v>
+      </c>
+      <c r="E10" t="s">
+        <v>39</v>
       </c>
     </row>
   </sheetData>
-  <pageMargins bottom="1" footer="0.5" header="0.5" left="0.75" right="0.75" top="1"/>
+  <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
+  <headerFooter/>
 </worksheet>
 </file>
--- a/Configs/skill_pool_config.xlsx
+++ b/Configs/skill_pool_config.xlsx
@@ -27,7 +27,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="42" uniqueCount="40">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="62" uniqueCount="58">
   <si>
     <t>id</t>
   </si>
@@ -35,7 +35,13 @@
     <t>name</t>
   </si>
   <si>
-    <t>desList</t>
+    <t>des</t>
+  </si>
+  <si>
+    <t>upDes</t>
+  </si>
+  <si>
+    <t>levelDes</t>
   </si>
   <si>
     <t>icon</t>
@@ -50,13 +56,19 @@
     <t>string</t>
   </si>
   <si>
-    <t>string[]</t>
+    <t>{int level;string des}[]</t>
   </si>
   <si>
     <t>烈焰圣弹</t>
   </si>
   <si>
-    <t>发射炽热的火焰弹|[升级效果]额外发射一枚|[6级]附加灼烧，每秒造成30%火伤，持续5秒|[10级]命中后会发生爆炸</t>
+    <t>发射炽热的火焰弹，造成100%火伤</t>
+  </si>
+  <si>
+    <t>提升10%火伤</t>
+  </si>
+  <si>
+    <t>3~子弹变为散射4次|5~子弹变为散射8次|8~附加灼烧，每秒造成30%火伤，持续5秒|10~命中后会发生爆炸造成50%火伤</t>
   </si>
   <si>
     <t>Icon/commet-128</t>
@@ -68,7 +80,13 @@
     <t>治愈圣火</t>
   </si>
   <si>
-    <t>恢复生命最大生命值的10%|[升级效果]多恢复最大生命值的5%|[6级]附加持续恢复，每秒恢复已损失生命值的10%，持续10秒|[10级]附加减伤</t>
+    <t>信仰浓烈的火焰可以治愈身体，恢复相当于攻击力30%的血量</t>
+  </si>
+  <si>
+    <t>恢复量提升5%</t>
+  </si>
+  <si>
+    <t>3~额外恢复最大生命值的10%|5~额外恢复最大生命值的20%|8~附加持续恢复，每秒恢复相当于攻击力20%的生命值，持续10秒|10~附加50%减伤效果，持续10秒</t>
   </si>
   <si>
     <t>Icon/potion-pink-1-128</t>
@@ -80,7 +98,13 @@
     <t>急冻冰锥</t>
   </si>
   <si>
-    <t>发射冰棱并冰冻|[升级效果]额外发射一枚|[6级]子弹变为穿刺效果|[10级]冰冻时间提升至10秒</t>
+    <t>发射冰棱，使命中的敌人冰冻2秒，造成75%冰伤</t>
+  </si>
+  <si>
+    <t>提升10%冰伤</t>
+  </si>
+  <si>
+    <t>3~子弹变为散射五次|5~冰冻时间提升至5秒|8~子弹具有穿刺效果|10~冰冻时间提升至15秒，并且受到伤害提升30%</t>
   </si>
   <si>
     <t>Icon/skull-128</t>
@@ -89,10 +113,16 @@
     <t>松开发射冰锥</t>
   </si>
   <si>
-    <t>血能交换</t>
-  </si>
-  <si>
-    <t>消耗当前生命值的25%换取随机一个非满级技能的10点经验|[升级效果]获得经验值提升5点|[6级]随机三个非满级技能|[10级]改为所有非满级技能</t>
+    <t>能量泉源</t>
+  </si>
+  <si>
+    <t>消耗生命源力换取先知之力，损失当前生命值的50%获得随机两个非满级技能的20点经验</t>
+  </si>
+  <si>
+    <t>额外获得5点经验值</t>
+  </si>
+  <si>
+    <t>3~损失生命值降为25%|5~为随机三个技能提供经验|8~不再损失生命值|10~为随机四个技能提供经验</t>
   </si>
   <si>
     <t>Icon/solar-system-1-128</t>
@@ -104,7 +134,13 @@
     <t>闪电连锁</t>
   </si>
   <si>
-    <t>发射一枚闪电，命中后弹射向另一名敌人，每次弹射伤害递减10%，最多递减50%|[升级效果]次数弹射加一次|[6级]减速50%，持续3秒|[10级]闪电伤害不衰减</t>
+    <t>发射一枚闪电，造成10%电伤，命中后弹射向另一名敌人，可以弹射5次，每次弹射伤害递减20%，最多递减至30%</t>
+  </si>
+  <si>
+    <t>提升10%电伤</t>
+  </si>
+  <si>
+    <t>3~造成减速50%，持续3秒|5~弹射次数提升至15次|8~弹射伤害不再衰减|10~命中产生雷暴造成10%电伤</t>
   </si>
   <si>
     <t>Icon/satellite-128</t>
@@ -116,7 +152,13 @@
     <t>电磁盾牌</t>
   </si>
   <si>
-    <t>为自身附加一共最大生命值10%的护盾，护盾被攻击时会反射一枚子弹造成30%电伤|[升级效果]护盾提升5%，反射子弹数量加一|[6级]反射的子弹具有穿透效果|[10级]护盾破裂时，对敌人造成击退，并且恢复自身已损失生命值的50%</t>
+    <t>生成一个电磁盾牌，自身附加最大生命值10%的护盾</t>
+  </si>
+  <si>
+    <t>护盾值额外提升5%</t>
+  </si>
+  <si>
+    <t>3~受到攻击时，反击散射3枚子弹，每个造成30%电伤|5~反击的子弹增加到10颗|8~反击的子弹具有穿透效果|10~护盾破裂时，对敌人造成击退，并且恢复自身已损失生命值的50%</t>
   </si>
   <si>
     <t>Icon/gem-2-128</t>
@@ -128,7 +170,13 @@
     <t>超暴风</t>
   </si>
   <si>
-    <t>对所有敌人造成100%的风伤并击退|[升级效果]+10%击退|[6级]附加减速|[10级]附加易伤</t>
+    <t>召唤风暴，对所有敌人造成30%的风伤</t>
+  </si>
+  <si>
+    <t>提升5%风伤</t>
+  </si>
+  <si>
+    <t>3~造成击退效果，5~击退后造成30%减速，持续10秒|8~造成巨额击退效果|10~附加受到伤害增加50%，持续5秒</t>
   </si>
   <si>
     <t>Icon/black-hole-128</t>
@@ -140,7 +188,13 @@
     <t>风影守卫</t>
   </si>
   <si>
-    <t>召唤风影战斗，继承主角25%属性|[升级效果]持续+2秒|[6级]追踪弹|[10级]额外两个风影</t>
+    <t>召唤风影守卫帮助战斗，继承主角25%属性，持续5秒</t>
+  </si>
+  <si>
+    <t>召唤物持续时间+1秒</t>
+  </si>
+  <si>
+    <t>3~继承属性提升至50%，5~子弹效果变为追踪|8~子弹最多可以穿刺两个目标|10~额外召唤两个风影守卫</t>
   </si>
   <si>
     <t>Icon/alien-128</t>
@@ -159,14 +213,7 @@
     <numFmt numFmtId="43" formatCode="_ * #,##0.00_ ;_ * \-#,##0.00_ ;_ * &quot;-&quot;??_ ;_ @_ "/>
     <numFmt numFmtId="44" formatCode="_ &quot;￥&quot;* #,##0.00_ ;_ &quot;￥&quot;* \-#,##0.00_ ;_ &quot;￥&quot;* &quot;-&quot;??_ ;_ @_ "/>
   </numFmts>
-  <fonts count="21">
-    <font>
-      <sz val="11"/>
-      <color theme="1"/>
-      <name val="宋体"/>
-      <charset val="134"/>
-      <scheme val="minor"/>
-    </font>
+  <fonts count="20">
     <font>
       <sz val="11"/>
       <color theme="1"/>
@@ -622,153 +669,159 @@
   </borders>
   <cellStyleXfs count="49">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0"/>
-    <xf numFmtId="43" fontId="1" fillId="0" borderId="0" applyFont="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="44" fontId="1" fillId="0" borderId="0" applyFont="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="9" fontId="1" fillId="0" borderId="0" applyFont="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="41" fontId="1" fillId="0" borderId="0" applyFont="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="42" fontId="1" fillId="0" borderId="0" applyFont="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+    <xf numFmtId="43" fontId="0" fillId="0" borderId="0" applyFont="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="44" fontId="0" fillId="0" borderId="0" applyFont="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="9" fontId="0" fillId="0" borderId="0" applyFont="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="41" fontId="0" fillId="0" borderId="0" applyFont="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="42" fontId="0" fillId="0" borderId="0" applyFont="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="1" fillId="0" borderId="0" applyNumberFormat="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
     <xf numFmtId="0" fontId="2" fillId="0" borderId="0" applyNumberFormat="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
+    <xf numFmtId="0" fontId="0" fillId="2" borderId="1" applyNumberFormat="0" applyFont="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
     <xf numFmtId="0" fontId="3" fillId="0" borderId="0" applyNumberFormat="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="1" fillId="2" borderId="1" applyNumberFormat="0" applyFont="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
     <xf numFmtId="0" fontId="4" fillId="0" borderId="0" applyNumberFormat="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
     <xf numFmtId="0" fontId="5" fillId="0" borderId="0" applyNumberFormat="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="6" fillId="0" borderId="0" applyNumberFormat="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+    <xf numFmtId="0" fontId="6" fillId="0" borderId="2" applyNumberFormat="0" applyFill="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
     <xf numFmtId="0" fontId="7" fillId="0" borderId="2" applyNumberFormat="0" applyFill="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="8" fillId="0" borderId="2" applyNumberFormat="0" applyFill="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="9" fillId="0" borderId="3" applyNumberFormat="0" applyFill="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="9" fillId="0" borderId="0" applyNumberFormat="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="10" fillId="3" borderId="4" applyNumberFormat="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="11" fillId="4" borderId="5" applyNumberFormat="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="12" fillId="4" borderId="4" applyNumberFormat="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="13" fillId="5" borderId="6" applyNumberFormat="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="14" fillId="0" borderId="7" applyNumberFormat="0" applyFill="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="15" fillId="0" borderId="8" applyNumberFormat="0" applyFill="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="16" fillId="6" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="17" fillId="7" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="18" fillId="8" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="19" fillId="9" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="20" fillId="10" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="20" fillId="11" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="19" fillId="12" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="19" fillId="13" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="20" fillId="14" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="20" fillId="15" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="19" fillId="16" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="19" fillId="17" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="20" fillId="18" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="20" fillId="19" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="19" fillId="20" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="19" fillId="21" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="20" fillId="22" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="20" fillId="23" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="19" fillId="24" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="19" fillId="25" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="20" fillId="26" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="20" fillId="27" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="19" fillId="28" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="19" fillId="29" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="20" fillId="30" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="20" fillId="31" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="19" fillId="32" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+    <xf numFmtId="0" fontId="8" fillId="0" borderId="3" applyNumberFormat="0" applyFill="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="8" fillId="0" borderId="0" applyNumberFormat="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="9" fillId="3" borderId="4" applyNumberFormat="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="10" fillId="4" borderId="5" applyNumberFormat="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="11" fillId="4" borderId="4" applyNumberFormat="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="12" fillId="5" borderId="6" applyNumberFormat="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="13" fillId="0" borderId="7" applyNumberFormat="0" applyFill="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="14" fillId="0" borderId="8" applyNumberFormat="0" applyFill="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="15" fillId="6" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="16" fillId="7" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="17" fillId="8" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="18" fillId="9" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="19" fillId="10" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="19" fillId="11" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="18" fillId="12" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="18" fillId="13" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="19" fillId="14" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="19" fillId="15" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="18" fillId="16" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="18" fillId="17" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="19" fillId="18" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="19" fillId="19" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="18" fillId="20" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="18" fillId="21" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="19" fillId="22" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="19" fillId="23" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="18" fillId="24" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="18" fillId="25" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="19" fillId="26" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="19" fillId="27" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="18" fillId="28" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="18" fillId="29" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="19" fillId="30" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="19" fillId="31" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="18" fillId="32" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
   </cellStyleXfs>
-  <cellXfs count="1">
+  <cellXfs count="3">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0"/>
+    <xf numFmtId="49" fontId="0" fillId="0" borderId="0" xfId="0" applyNumberFormat="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="49" fontId="0" fillId="0" borderId="0" xfId="0" applyNumberFormat="1" applyAlignment="1">
+      <alignment vertical="center"/>
+    </xf>
   </cellXfs>
   <cellStyles count="49">
     <cellStyle name="常规" xfId="0" builtinId="0"/>
@@ -1115,182 +1168,246 @@
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:xdr="http://schemas.openxmlformats.org/drawingml/2006/spreadsheetDrawing" xmlns:x14="http://schemas.microsoft.com/office/spreadsheetml/2009/9/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:etc="http://www.wps.cn/officeDocument/2017/etCustomData">
   <sheetPr/>
-  <dimension ref="A1:E10"/>
-  <sheetFormatPr defaultColWidth="9" defaultRowHeight="13.5" outlineLevelCol="4"/>
+  <dimension ref="A1:G10"/>
+  <sheetFormatPr defaultColWidth="9" defaultRowHeight="13.5" outlineLevelCol="6"/>
   <cols>
-    <col min="3" max="3" width="50.125" customWidth="1"/>
-    <col min="4" max="4" width="26" customWidth="1"/>
-    <col min="5" max="5" width="12.875" customWidth="1"/>
+    <col min="1" max="2" width="9" style="1"/>
+    <col min="3" max="3" width="32.75" style="1" customWidth="1"/>
+    <col min="4" max="4" width="26" style="1" customWidth="1"/>
+    <col min="5" max="5" width="42.5" style="1" customWidth="1"/>
+    <col min="6" max="6" width="26" style="1" customWidth="1"/>
+    <col min="7" max="7" width="12.875" style="1" customWidth="1"/>
+    <col min="8" max="16384" width="9" style="1"/>
   </cols>
   <sheetData>
-    <row r="1" spans="1:5">
-      <c r="A1" t="s">
+    <row r="1" spans="1:7">
+      <c r="A1" s="1" t="s">
         <v>0</v>
       </c>
-      <c r="B1" t="s">
+      <c r="B1" s="1" t="s">
         <v>1</v>
       </c>
-      <c r="C1" t="s">
+      <c r="C1" s="1" t="s">
         <v>2</v>
       </c>
-      <c r="D1" t="s">
+      <c r="D1" s="1" t="s">
         <v>3</v>
       </c>
-      <c r="E1" t="s">
+      <c r="E1" s="1" t="s">
         <v>4</v>
       </c>
+      <c r="F1" s="1" t="s">
+        <v>5</v>
+      </c>
+      <c r="G1" s="1" t="s">
+        <v>6</v>
+      </c>
     </row>
-    <row r="2" spans="1:5">
-      <c r="A2" t="s">
-        <v>5</v>
-      </c>
-      <c r="B2" t="s">
-        <v>6</v>
-      </c>
-      <c r="C2" t="s">
+    <row r="2" spans="1:7">
+      <c r="A2" s="1" t="s">
         <v>7</v>
       </c>
-      <c r="D2" t="s">
-        <v>6</v>
-      </c>
-      <c r="E2" t="s">
-        <v>6</v>
+      <c r="B2" s="1" t="s">
+        <v>8</v>
+      </c>
+      <c r="C2" s="1" t="s">
+        <v>8</v>
+      </c>
+      <c r="D2" s="1" t="s">
+        <v>8</v>
+      </c>
+      <c r="E2" s="1" t="s">
+        <v>9</v>
+      </c>
+      <c r="F2" s="1" t="s">
+        <v>8</v>
+      </c>
+      <c r="G2" s="1" t="s">
+        <v>8</v>
       </c>
     </row>
-    <row r="3" spans="1:5">
-      <c r="A3">
+    <row r="3" ht="40.5" spans="1:7">
+      <c r="A3" s="1">
         <v>1001</v>
       </c>
-      <c r="B3" t="s">
-        <v>8</v>
-      </c>
-      <c r="C3" t="s">
-        <v>9</v>
-      </c>
-      <c r="D3" t="s">
+      <c r="B3" s="1" t="s">
         <v>10</v>
       </c>
-      <c r="E3" t="s">
+      <c r="C3" s="1" t="s">
         <v>11</v>
       </c>
+      <c r="D3" s="1" t="s">
+        <v>12</v>
+      </c>
+      <c r="E3" s="1" t="s">
+        <v>13</v>
+      </c>
+      <c r="F3" s="1" t="s">
+        <v>14</v>
+      </c>
+      <c r="G3" s="1" t="s">
+        <v>15</v>
+      </c>
     </row>
-    <row r="4" spans="1:5">
-      <c r="A4">
+    <row r="4" ht="54" spans="1:7">
+      <c r="A4" s="1">
         <v>1002</v>
       </c>
-      <c r="B4" t="s">
-        <v>12</v>
-      </c>
-      <c r="C4" t="s">
-        <v>13</v>
-      </c>
-      <c r="D4" t="s">
-        <v>14</v>
-      </c>
-      <c r="E4" t="s">
-        <v>15</v>
+      <c r="B4" s="1" t="s">
+        <v>16</v>
+      </c>
+      <c r="C4" s="1" t="s">
+        <v>17</v>
+      </c>
+      <c r="D4" s="1" t="s">
+        <v>18</v>
+      </c>
+      <c r="E4" s="1" t="s">
+        <v>19</v>
+      </c>
+      <c r="F4" s="1" t="s">
+        <v>20</v>
+      </c>
+      <c r="G4" s="1" t="s">
+        <v>21</v>
       </c>
     </row>
-    <row r="5" spans="1:5">
-      <c r="A5">
+    <row r="5" ht="40.5" spans="1:7">
+      <c r="A5" s="1">
         <v>1003</v>
       </c>
-      <c r="B5" t="s">
-        <v>16</v>
-      </c>
-      <c r="C5" t="s">
-        <v>17</v>
-      </c>
-      <c r="D5" t="s">
-        <v>18</v>
-      </c>
-      <c r="E5" t="s">
-        <v>19</v>
+      <c r="B5" s="1" t="s">
+        <v>22</v>
+      </c>
+      <c r="C5" s="1" t="s">
+        <v>23</v>
+      </c>
+      <c r="D5" s="1" t="s">
+        <v>24</v>
+      </c>
+      <c r="E5" s="1" t="s">
+        <v>25</v>
+      </c>
+      <c r="F5" s="1" t="s">
+        <v>26</v>
+      </c>
+      <c r="G5" s="1" t="s">
+        <v>27</v>
       </c>
     </row>
-    <row r="6" spans="1:5">
-      <c r="A6">
+    <row r="6" ht="40.5" spans="1:7">
+      <c r="A6" s="1">
         <v>1004</v>
       </c>
-      <c r="B6" t="s">
-        <v>20</v>
-      </c>
-      <c r="C6" t="s">
-        <v>21</v>
-      </c>
-      <c r="D6" t="s">
-        <v>22</v>
-      </c>
-      <c r="E6" t="s">
-        <v>23</v>
+      <c r="B6" s="2" t="s">
+        <v>28</v>
+      </c>
+      <c r="C6" s="1" t="s">
+        <v>29</v>
+      </c>
+      <c r="D6" s="1" t="s">
+        <v>30</v>
+      </c>
+      <c r="E6" s="1" t="s">
+        <v>31</v>
+      </c>
+      <c r="F6" s="1" t="s">
+        <v>32</v>
+      </c>
+      <c r="G6" s="1" t="s">
+        <v>33</v>
       </c>
     </row>
-    <row r="7" spans="1:5">
-      <c r="A7">
+    <row r="7" ht="40.5" spans="1:7">
+      <c r="A7" s="1">
         <v>1005</v>
       </c>
-      <c r="B7" t="s">
-        <v>24</v>
-      </c>
-      <c r="C7" t="s">
-        <v>25</v>
-      </c>
-      <c r="D7" t="s">
-        <v>26</v>
-      </c>
-      <c r="E7" t="s">
-        <v>27</v>
+      <c r="B7" s="1" t="s">
+        <v>34</v>
+      </c>
+      <c r="C7" s="1" t="s">
+        <v>35</v>
+      </c>
+      <c r="D7" s="1" t="s">
+        <v>36</v>
+      </c>
+      <c r="E7" s="1" t="s">
+        <v>37</v>
+      </c>
+      <c r="F7" s="1" t="s">
+        <v>38</v>
+      </c>
+      <c r="G7" s="1" t="s">
+        <v>39</v>
       </c>
     </row>
-    <row r="8" spans="1:5">
-      <c r="A8">
+    <row r="8" ht="54" spans="1:7">
+      <c r="A8" s="1">
         <v>1006</v>
       </c>
-      <c r="B8" t="s">
-        <v>28</v>
-      </c>
-      <c r="C8" t="s">
-        <v>29</v>
-      </c>
-      <c r="D8" t="s">
-        <v>30</v>
-      </c>
-      <c r="E8" t="s">
-        <v>31</v>
+      <c r="B8" s="1" t="s">
+        <v>40</v>
+      </c>
+      <c r="C8" s="1" t="s">
+        <v>41</v>
+      </c>
+      <c r="D8" s="1" t="s">
+        <v>42</v>
+      </c>
+      <c r="E8" s="1" t="s">
+        <v>43</v>
+      </c>
+      <c r="F8" s="1" t="s">
+        <v>44</v>
+      </c>
+      <c r="G8" s="1" t="s">
+        <v>45</v>
       </c>
     </row>
-    <row r="9" spans="1:5">
-      <c r="A9">
+    <row r="9" ht="40.5" spans="1:7">
+      <c r="A9" s="1">
         <v>1007</v>
       </c>
-      <c r="B9" t="s">
-        <v>32</v>
-      </c>
-      <c r="C9" t="s">
-        <v>33</v>
-      </c>
-      <c r="D9" t="s">
-        <v>34</v>
-      </c>
-      <c r="E9" t="s">
-        <v>35</v>
+      <c r="B9" s="1" t="s">
+        <v>46</v>
+      </c>
+      <c r="C9" s="1" t="s">
+        <v>47</v>
+      </c>
+      <c r="D9" s="1" t="s">
+        <v>48</v>
+      </c>
+      <c r="E9" s="1" t="s">
+        <v>49</v>
+      </c>
+      <c r="F9" s="1" t="s">
+        <v>50</v>
+      </c>
+      <c r="G9" s="1" t="s">
+        <v>51</v>
       </c>
     </row>
-    <row r="10" spans="1:5">
-      <c r="A10">
+    <row r="10" ht="40.5" spans="1:7">
+      <c r="A10" s="1">
         <v>1008</v>
       </c>
-      <c r="B10" t="s">
-        <v>36</v>
-      </c>
-      <c r="C10" t="s">
-        <v>37</v>
-      </c>
-      <c r="D10" t="s">
-        <v>38</v>
-      </c>
-      <c r="E10" t="s">
-        <v>39</v>
+      <c r="B10" s="1" t="s">
+        <v>52</v>
+      </c>
+      <c r="C10" s="1" t="s">
+        <v>53</v>
+      </c>
+      <c r="D10" s="1" t="s">
+        <v>54</v>
+      </c>
+      <c r="E10" s="1" t="s">
+        <v>55</v>
+      </c>
+      <c r="F10" s="1" t="s">
+        <v>56</v>
+      </c>
+      <c r="G10" s="1" t="s">
+        <v>57</v>
       </c>
     </row>
   </sheetData>
